--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1849,53 +1849,53 @@
     <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
+</t>
+  </si>
+  <si>
+    <t>Médicament</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.realmCode</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.displayable</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.root</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.extension</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.templateId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeCode</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
+  </si>
+  <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Médicament</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.realmCode</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.displayable</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.root</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.extension</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.templateId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeCode</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct
 </t>
   </si>
   <si>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13703" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13703" uniqueCount="845">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1582,6 +1582,10 @@
 L'argument @value permet d'indiquer la quantité de produit à administrer.
 L'argument @unit permet d'indiquer le rythme d'administration en combinant l'unité de quantité et l'unité de temps (séparés par le caractère ‘/'). Les unités sont exprimées selon le système de codage UCUM.
 Dans chaque élément 'low' et 'high', un élément 'translation' peut permettre de pointer sur l'élément de la partie narrative relative à cette information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fr-rateQuantity-traitement:Le rythme d'administration porte soit un nullFlavor, soit les sous-éléments low et high. {nullFlavor.exists() or (low.exists() and high.exists())}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.rateQuantity.nullFlavor</t>
@@ -24803,7 +24807,7 @@
         <v>75</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>75</v>
+        <v>506</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>75</v>
@@ -24811,10 +24815,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24912,10 +24916,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -25015,10 +25019,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -25118,10 +25122,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -25221,10 +25225,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -25320,10 +25324,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -25333,7 +25337,7 @@
         <v>428</v>
       </c>
       <c r="F219" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G219" t="s" s="2">
         <v>76</v>
@@ -25423,10 +25427,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -25524,10 +25528,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25627,10 +25631,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25730,10 +25734,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25833,10 +25837,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25934,10 +25938,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -26037,10 +26041,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -26140,10 +26144,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -26243,10 +26247,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -26346,10 +26350,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -26449,10 +26453,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -26550,10 +26554,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -26651,10 +26655,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -26754,10 +26758,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26855,10 +26859,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26956,10 +26960,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -27059,10 +27063,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -27160,10 +27164,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -27263,10 +27267,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -27364,10 +27368,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -27461,10 +27465,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -27566,10 +27570,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -27669,10 +27673,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -27772,10 +27776,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -27875,10 +27879,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27978,10 +27982,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -28081,10 +28085,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -28182,10 +28186,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -28285,10 +28289,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -28388,10 +28392,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -28401,7 +28405,7 @@
         <v>474</v>
       </c>
       <c r="F249" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G249" t="s" s="2">
         <v>76</v>
@@ -28491,10 +28495,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -28592,10 +28596,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -28695,10 +28699,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -28798,10 +28802,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -28901,10 +28905,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -29002,10 +29006,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -29105,10 +29109,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -29208,10 +29212,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -29311,10 +29315,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -29414,10 +29418,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -29517,10 +29521,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -29618,10 +29622,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -29719,10 +29723,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -29822,10 +29826,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -29923,10 +29927,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -30024,10 +30028,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -30127,10 +30131,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -30228,10 +30232,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -30331,10 +30335,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -30432,10 +30436,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -30529,10 +30533,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -30634,10 +30638,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -30737,10 +30741,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -30840,10 +30844,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -30943,10 +30947,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -31046,10 +31050,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -31149,10 +31153,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -31250,10 +31254,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -31276,10 +31280,10 @@
         <v>75</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M277" s="2"/>
       <c r="N277" s="2"/>
@@ -31331,7 +31335,7 @@
         <v>75</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>81</v>
@@ -31351,10 +31355,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -31452,17 +31456,17 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E279" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F279" t="s" s="2">
         <v>76</v>
@@ -31484,7 +31488,7 @@
       </c>
       <c r="L279" s="2"/>
       <c r="M279" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N279" s="2"/>
       <c r="O279" s="2"/>
@@ -31535,7 +31539,7 @@
         <v>75</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>
@@ -31555,10 +31559,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -31656,10 +31660,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -31759,10 +31763,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -31862,10 +31866,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -31965,17 +31969,17 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E284" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F284" t="s" s="2">
         <v>76</v>
@@ -31997,7 +32001,7 @@
       </c>
       <c r="L284" s="2"/>
       <c r="M284" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
@@ -32048,7 +32052,7 @@
         <v>75</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>81</v>
@@ -32068,10 +32072,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -32169,10 +32173,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -32272,10 +32276,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -32375,10 +32379,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -32478,10 +32482,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -32537,25 +32541,25 @@
       </c>
       <c r="Y289" s="2"/>
       <c r="Z289" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AA289" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB289" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC289" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD289" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE289" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF289" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AA289" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB289" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC289" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD289" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE289" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF289" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>81</v>
@@ -32575,10 +32579,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -32601,13 +32605,13 @@
         <v>75</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" s="2"/>
@@ -32658,7 +32662,7 @@
         <v>75</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>76</v>
@@ -32678,10 +32682,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -32779,10 +32783,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -32880,10 +32884,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -32981,10 +32985,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -33082,10 +33086,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -33185,10 +33189,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -33288,10 +33292,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -33391,10 +33395,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -33494,10 +33498,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -33595,10 +33599,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -33632,7 +33636,7 @@
       </c>
       <c r="Q300" s="2"/>
       <c r="R300" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="S300" t="s" s="2">
         <v>75</v>
@@ -33654,7 +33658,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>75</v>
@@ -33672,7 +33676,7 @@
         <v>75</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>81</v>
@@ -33692,10 +33696,10 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -33718,7 +33722,7 @@
         <v>75</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L301" s="2"/>
       <c r="M301" s="2"/>
@@ -33771,7 +33775,7 @@
         <v>75</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG301" t="s" s="2">
         <v>76</v>
@@ -33791,10 +33795,10 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -33817,7 +33821,7 @@
         <v>75</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L302" s="2"/>
       <c r="M302" s="2"/>
@@ -33870,7 +33874,7 @@
         <v>75</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>81</v>
@@ -33890,10 +33894,10 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -33916,7 +33920,7 @@
         <v>75</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L303" s="2"/>
       <c r="M303" s="2"/>
@@ -33969,7 +33973,7 @@
         <v>75</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>81</v>
@@ -33989,10 +33993,10 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -34015,7 +34019,7 @@
         <v>75</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L304" s="2"/>
       <c r="M304" s="2"/>
@@ -34068,7 +34072,7 @@
         <v>75</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>81</v>
@@ -34088,10 +34092,10 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -34114,7 +34118,7 @@
         <v>75</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L305" s="2"/>
       <c r="M305" s="2"/>
@@ -34167,7 +34171,7 @@
         <v>75</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>81</v>
@@ -34187,10 +34191,10 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
@@ -34213,7 +34217,7 @@
         <v>75</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L306" s="2"/>
       <c r="M306" s="2"/>
@@ -34266,7 +34270,7 @@
         <v>75</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>81</v>
@@ -34286,10 +34290,10 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
@@ -34312,7 +34316,7 @@
         <v>75</v>
       </c>
       <c r="K307" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L307" s="2"/>
       <c r="M307" s="2"/>
@@ -34365,7 +34369,7 @@
         <v>75</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>81</v>
@@ -34385,10 +34389,10 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -34411,7 +34415,7 @@
         <v>75</v>
       </c>
       <c r="K308" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L308" s="2"/>
       <c r="M308" s="2"/>
@@ -34452,7 +34456,7 @@
         <v>75</v>
       </c>
       <c r="AB308" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AC308" s="2"/>
       <c r="AD308" t="s" s="2">
@@ -34462,7 +34466,7 @@
         <v>127</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>81</v>
@@ -34482,13 +34486,13 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D309" t="s" s="2">
         <v>75</v>
@@ -34510,13 +34514,13 @@
         <v>75</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N309" s="2"/>
       <c r="O309" s="2"/>
@@ -34567,7 +34571,7 @@
         <v>75</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>81</v>
@@ -34587,10 +34591,10 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -34688,10 +34692,10 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
@@ -34789,10 +34793,10 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -34890,10 +34894,10 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -34991,10 +34995,10 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -35094,10 +35098,10 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -35197,10 +35201,10 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
@@ -35300,10 +35304,10 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -35403,10 +35407,10 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
@@ -35504,10 +35508,10 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
@@ -35544,7 +35548,7 @@
         <v>75</v>
       </c>
       <c r="S319" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="T319" t="s" s="2">
         <v>75</v>
@@ -35563,7 +35567,7 @@
       </c>
       <c r="Y319" s="2"/>
       <c r="Z319" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA319" t="s" s="2">
         <v>75</v>
@@ -35581,7 +35585,7 @@
         <v>75</v>
       </c>
       <c r="AF319" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG319" t="s" s="2">
         <v>76</v>
@@ -35601,10 +35605,10 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
@@ -35631,7 +35635,7 @@
       </c>
       <c r="L320" s="2"/>
       <c r="M320" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N320" s="2"/>
       <c r="O320" s="2"/>
@@ -35682,7 +35686,7 @@
         <v>75</v>
       </c>
       <c r="AF320" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG320" t="s" s="2">
         <v>81</v>
@@ -35702,10 +35706,10 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
@@ -35732,7 +35736,7 @@
       </c>
       <c r="L321" s="2"/>
       <c r="M321" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N321" s="2"/>
       <c r="O321" s="2"/>
@@ -35783,7 +35787,7 @@
         <v>75</v>
       </c>
       <c r="AF321" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG321" t="s" s="2">
         <v>81</v>
@@ -35803,10 +35807,10 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
@@ -35882,7 +35886,7 @@
         <v>75</v>
       </c>
       <c r="AF322" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG322" t="s" s="2">
         <v>81</v>
@@ -35902,10 +35906,10 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
@@ -35928,7 +35932,7 @@
         <v>75</v>
       </c>
       <c r="K323" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L323" s="2"/>
       <c r="M323" s="2"/>
@@ -35981,7 +35985,7 @@
         <v>75</v>
       </c>
       <c r="AF323" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG323" t="s" s="2">
         <v>81</v>
@@ -36001,10 +36005,10 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
@@ -36027,7 +36031,7 @@
         <v>75</v>
       </c>
       <c r="K324" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L324" s="2"/>
       <c r="M324" s="2"/>
@@ -36080,7 +36084,7 @@
         <v>75</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>81</v>
@@ -36100,10 +36104,10 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" t="s" s="2">
@@ -36126,7 +36130,7 @@
         <v>75</v>
       </c>
       <c r="K325" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L325" s="2"/>
       <c r="M325" s="2"/>
@@ -36179,7 +36183,7 @@
         <v>75</v>
       </c>
       <c r="AF325" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG325" t="s" s="2">
         <v>81</v>
@@ -36199,10 +36203,10 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" t="s" s="2">
@@ -36225,7 +36229,7 @@
         <v>75</v>
       </c>
       <c r="K326" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L326" s="2"/>
       <c r="M326" s="2"/>
@@ -36278,7 +36282,7 @@
         <v>75</v>
       </c>
       <c r="AF326" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG326" t="s" s="2">
         <v>81</v>
@@ -36298,10 +36302,10 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
@@ -36324,7 +36328,7 @@
         <v>75</v>
       </c>
       <c r="K327" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L327" s="2"/>
       <c r="M327" s="2"/>
@@ -36377,7 +36381,7 @@
         <v>75</v>
       </c>
       <c r="AF327" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG327" t="s" s="2">
         <v>81</v>
@@ -36397,10 +36401,10 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
@@ -36423,7 +36427,7 @@
         <v>75</v>
       </c>
       <c r="K328" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L328" s="2"/>
       <c r="M328" s="2"/>
@@ -36476,7 +36480,7 @@
         <v>75</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG328" t="s" s="2">
         <v>81</v>
@@ -36496,10 +36500,10 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" t="s" s="2">
@@ -36522,7 +36526,7 @@
         <v>75</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L329" s="2"/>
       <c r="M329" s="2"/>
@@ -36575,7 +36579,7 @@
         <v>75</v>
       </c>
       <c r="AF329" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG329" t="s" s="2">
         <v>81</v>
@@ -36595,10 +36599,10 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" t="s" s="2">
@@ -36621,7 +36625,7 @@
         <v>75</v>
       </c>
       <c r="K330" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L330" s="2"/>
       <c r="M330" s="2"/>
@@ -36674,7 +36678,7 @@
         <v>75</v>
       </c>
       <c r="AF330" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG330" t="s" s="2">
         <v>81</v>
@@ -36694,10 +36698,10 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
@@ -36720,7 +36724,7 @@
         <v>75</v>
       </c>
       <c r="K331" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L331" s="2"/>
       <c r="M331" s="2"/>
@@ -36773,7 +36777,7 @@
         <v>75</v>
       </c>
       <c r="AF331" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG331" t="s" s="2">
         <v>81</v>
@@ -36793,10 +36797,10 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" t="s" s="2">
@@ -36819,7 +36823,7 @@
         <v>75</v>
       </c>
       <c r="K332" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L332" s="2"/>
       <c r="M332" s="2"/>
@@ -36872,7 +36876,7 @@
         <v>75</v>
       </c>
       <c r="AF332" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG332" t="s" s="2">
         <v>81</v>
@@ -36892,10 +36896,10 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
@@ -36918,7 +36922,7 @@
         <v>75</v>
       </c>
       <c r="K333" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L333" s="2"/>
       <c r="M333" s="2"/>
@@ -36971,7 +36975,7 @@
         <v>75</v>
       </c>
       <c r="AF333" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG333" t="s" s="2">
         <v>81</v>
@@ -36991,13 +36995,13 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D334" t="s" s="2">
         <v>75</v>
@@ -37019,7 +37023,7 @@
         <v>75</v>
       </c>
       <c r="K334" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L334" s="2"/>
       <c r="M334" s="2"/>
@@ -37072,7 +37076,7 @@
         <v>75</v>
       </c>
       <c r="AF334" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG334" t="s" s="2">
         <v>81</v>
@@ -37092,10 +37096,10 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
@@ -37193,10 +37197,10 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" t="s" s="2">
@@ -37294,10 +37298,10 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
@@ -37395,10 +37399,10 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
@@ -37496,10 +37500,10 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -37599,10 +37603,10 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" t="s" s="2">
@@ -37702,10 +37706,10 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
@@ -37805,10 +37809,10 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
@@ -37908,10 +37912,10 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
@@ -38009,10 +38013,10 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" t="s" s="2">
@@ -38049,7 +38053,7 @@
         <v>75</v>
       </c>
       <c r="S344" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="T344" t="s" s="2">
         <v>75</v>
@@ -38068,7 +38072,7 @@
       </c>
       <c r="Y344" s="2"/>
       <c r="Z344" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA344" t="s" s="2">
         <v>75</v>
@@ -38086,7 +38090,7 @@
         <v>75</v>
       </c>
       <c r="AF344" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG344" t="s" s="2">
         <v>76</v>
@@ -38106,10 +38110,10 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
@@ -38136,7 +38140,7 @@
       </c>
       <c r="L345" s="2"/>
       <c r="M345" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N345" s="2"/>
       <c r="O345" s="2"/>
@@ -38187,7 +38191,7 @@
         <v>75</v>
       </c>
       <c r="AF345" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG345" t="s" s="2">
         <v>81</v>
@@ -38207,10 +38211,10 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" t="s" s="2">
@@ -38237,7 +38241,7 @@
       </c>
       <c r="L346" s="2"/>
       <c r="M346" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N346" s="2"/>
       <c r="O346" s="2"/>
@@ -38288,7 +38292,7 @@
         <v>75</v>
       </c>
       <c r="AF346" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG346" t="s" s="2">
         <v>81</v>
@@ -38308,10 +38312,10 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" t="s" s="2">
@@ -38387,7 +38391,7 @@
         <v>75</v>
       </c>
       <c r="AF347" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG347" t="s" s="2">
         <v>81</v>
@@ -38407,10 +38411,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" t="s" s="2">
@@ -38433,7 +38437,7 @@
         <v>75</v>
       </c>
       <c r="K348" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L348" s="2"/>
       <c r="M348" s="2"/>
@@ -38486,7 +38490,7 @@
         <v>75</v>
       </c>
       <c r="AF348" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG348" t="s" s="2">
         <v>81</v>
@@ -38506,10 +38510,10 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" t="s" s="2">
@@ -38532,7 +38536,7 @@
         <v>75</v>
       </c>
       <c r="K349" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L349" s="2"/>
       <c r="M349" s="2"/>
@@ -38585,7 +38589,7 @@
         <v>75</v>
       </c>
       <c r="AF349" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG349" t="s" s="2">
         <v>81</v>
@@ -38605,10 +38609,10 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" t="s" s="2">
@@ -38631,7 +38635,7 @@
         <v>75</v>
       </c>
       <c r="K350" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L350" s="2"/>
       <c r="M350" s="2"/>
@@ -38684,7 +38688,7 @@
         <v>75</v>
       </c>
       <c r="AF350" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG350" t="s" s="2">
         <v>81</v>
@@ -38704,10 +38708,10 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" t="s" s="2">
@@ -38730,7 +38734,7 @@
         <v>75</v>
       </c>
       <c r="K351" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L351" s="2"/>
       <c r="M351" s="2"/>
@@ -38783,7 +38787,7 @@
         <v>75</v>
       </c>
       <c r="AF351" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG351" t="s" s="2">
         <v>81</v>
@@ -38803,10 +38807,10 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" t="s" s="2">
@@ -38829,7 +38833,7 @@
         <v>75</v>
       </c>
       <c r="K352" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L352" s="2"/>
       <c r="M352" s="2"/>
@@ -38882,7 +38886,7 @@
         <v>75</v>
       </c>
       <c r="AF352" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG352" t="s" s="2">
         <v>81</v>
@@ -38902,10 +38906,10 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" t="s" s="2">
@@ -38928,7 +38932,7 @@
         <v>75</v>
       </c>
       <c r="K353" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L353" s="2"/>
       <c r="M353" s="2"/>
@@ -38981,7 +38985,7 @@
         <v>75</v>
       </c>
       <c r="AF353" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG353" t="s" s="2">
         <v>81</v>
@@ -39001,10 +39005,10 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" t="s" s="2">
@@ -39027,7 +39031,7 @@
         <v>75</v>
       </c>
       <c r="K354" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L354" s="2"/>
       <c r="M354" s="2"/>
@@ -39080,7 +39084,7 @@
         <v>75</v>
       </c>
       <c r="AF354" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG354" t="s" s="2">
         <v>81</v>
@@ -39100,10 +39104,10 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" t="s" s="2">
@@ -39126,7 +39130,7 @@
         <v>75</v>
       </c>
       <c r="K355" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L355" s="2"/>
       <c r="M355" s="2"/>
@@ -39179,7 +39183,7 @@
         <v>75</v>
       </c>
       <c r="AF355" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG355" t="s" s="2">
         <v>81</v>
@@ -39199,10 +39203,10 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" t="s" s="2">
@@ -39225,7 +39229,7 @@
         <v>75</v>
       </c>
       <c r="K356" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L356" s="2"/>
       <c r="M356" s="2"/>
@@ -39278,7 +39282,7 @@
         <v>75</v>
       </c>
       <c r="AF356" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG356" t="s" s="2">
         <v>81</v>
@@ -39298,10 +39302,10 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" t="s" s="2">
@@ -39324,13 +39328,13 @@
         <v>75</v>
       </c>
       <c r="K357" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L357" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N357" s="2"/>
       <c r="O357" s="2"/>
@@ -39381,7 +39385,7 @@
         <v>75</v>
       </c>
       <c r="AF357" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG357" t="s" s="2">
         <v>81</v>
@@ -39401,10 +39405,10 @@
     </row>
     <row r="358" hidden="true">
       <c r="A358" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C358" s="2"/>
       <c r="D358" t="s" s="2">
@@ -39427,7 +39431,7 @@
         <v>75</v>
       </c>
       <c r="K358" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L358" s="2"/>
       <c r="M358" s="2"/>
@@ -39480,7 +39484,7 @@
         <v>75</v>
       </c>
       <c r="AF358" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG358" t="s" s="2">
         <v>81</v>
@@ -39500,13 +39504,13 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D359" t="s" s="2">
         <v>75</v>
@@ -39528,7 +39532,7 @@
         <v>75</v>
       </c>
       <c r="K359" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L359" s="2"/>
       <c r="M359" s="2"/>
@@ -39581,7 +39585,7 @@
         <v>75</v>
       </c>
       <c r="AF359" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG359" t="s" s="2">
         <v>81</v>
@@ -39601,10 +39605,10 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C360" s="2"/>
       <c r="D360" t="s" s="2">
@@ -39702,10 +39706,10 @@
     </row>
     <row r="361" hidden="true">
       <c r="A361" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C361" s="2"/>
       <c r="D361" t="s" s="2">
@@ -39803,10 +39807,10 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" t="s" s="2">
@@ -39904,10 +39908,10 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C363" s="2"/>
       <c r="D363" t="s" s="2">
@@ -40005,10 +40009,10 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C364" s="2"/>
       <c r="D364" t="s" s="2">
@@ -40108,10 +40112,10 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" t="s" s="2">
@@ -40211,10 +40215,10 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" t="s" s="2">
@@ -40314,10 +40318,10 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C367" s="2"/>
       <c r="D367" t="s" s="2">
@@ -40417,10 +40421,10 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C368" s="2"/>
       <c r="D368" t="s" s="2">
@@ -40518,10 +40522,10 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" t="s" s="2">
@@ -40558,7 +40562,7 @@
         <v>75</v>
       </c>
       <c r="S369" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T369" t="s" s="2">
         <v>75</v>
@@ -40577,7 +40581,7 @@
       </c>
       <c r="Y369" s="2"/>
       <c r="Z369" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA369" t="s" s="2">
         <v>75</v>
@@ -40595,7 +40599,7 @@
         <v>75</v>
       </c>
       <c r="AF369" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG369" t="s" s="2">
         <v>76</v>
@@ -40615,10 +40619,10 @@
     </row>
     <row r="370" hidden="true">
       <c r="A370" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C370" s="2"/>
       <c r="D370" t="s" s="2">
@@ -40645,7 +40649,7 @@
       </c>
       <c r="L370" s="2"/>
       <c r="M370" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N370" s="2"/>
       <c r="O370" s="2"/>
@@ -40696,7 +40700,7 @@
         <v>75</v>
       </c>
       <c r="AF370" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG370" t="s" s="2">
         <v>81</v>
@@ -40716,10 +40720,10 @@
     </row>
     <row r="371" hidden="true">
       <c r="A371" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C371" s="2"/>
       <c r="D371" t="s" s="2">
@@ -40746,7 +40750,7 @@
       </c>
       <c r="L371" s="2"/>
       <c r="M371" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N371" s="2"/>
       <c r="O371" s="2"/>
@@ -40797,7 +40801,7 @@
         <v>75</v>
       </c>
       <c r="AF371" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG371" t="s" s="2">
         <v>81</v>
@@ -40817,10 +40821,10 @@
     </row>
     <row r="372" hidden="true">
       <c r="A372" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C372" s="2"/>
       <c r="D372" t="s" s="2">
@@ -40896,7 +40900,7 @@
         <v>75</v>
       </c>
       <c r="AF372" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG372" t="s" s="2">
         <v>81</v>
@@ -40916,10 +40920,10 @@
     </row>
     <row r="373" hidden="true">
       <c r="A373" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C373" s="2"/>
       <c r="D373" t="s" s="2">
@@ -40942,7 +40946,7 @@
         <v>75</v>
       </c>
       <c r="K373" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L373" s="2"/>
       <c r="M373" s="2"/>
@@ -40995,7 +40999,7 @@
         <v>75</v>
       </c>
       <c r="AF373" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG373" t="s" s="2">
         <v>81</v>
@@ -41015,10 +41019,10 @@
     </row>
     <row r="374" hidden="true">
       <c r="A374" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C374" s="2"/>
       <c r="D374" t="s" s="2">
@@ -41041,7 +41045,7 @@
         <v>75</v>
       </c>
       <c r="K374" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L374" s="2"/>
       <c r="M374" s="2"/>
@@ -41094,7 +41098,7 @@
         <v>75</v>
       </c>
       <c r="AF374" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG374" t="s" s="2">
         <v>81</v>
@@ -41114,10 +41118,10 @@
     </row>
     <row r="375" hidden="true">
       <c r="A375" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C375" s="2"/>
       <c r="D375" t="s" s="2">
@@ -41140,13 +41144,13 @@
         <v>75</v>
       </c>
       <c r="K375" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N375" s="2"/>
       <c r="O375" s="2"/>
@@ -41197,7 +41201,7 @@
         <v>75</v>
       </c>
       <c r="AF375" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG375" t="s" s="2">
         <v>81</v>
@@ -41217,10 +41221,10 @@
     </row>
     <row r="376" hidden="true">
       <c r="A376" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C376" s="2"/>
       <c r="D376" t="s" s="2">
@@ -41243,7 +41247,7 @@
         <v>75</v>
       </c>
       <c r="K376" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L376" s="2"/>
       <c r="M376" s="2"/>
@@ -41296,7 +41300,7 @@
         <v>75</v>
       </c>
       <c r="AF376" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG376" t="s" s="2">
         <v>81</v>
@@ -41316,10 +41320,10 @@
     </row>
     <row r="377" hidden="true">
       <c r="A377" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C377" s="2"/>
       <c r="D377" t="s" s="2">
@@ -41342,7 +41346,7 @@
         <v>75</v>
       </c>
       <c r="K377" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L377" s="2"/>
       <c r="M377" s="2"/>
@@ -41395,7 +41399,7 @@
         <v>75</v>
       </c>
       <c r="AF377" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG377" t="s" s="2">
         <v>81</v>
@@ -41415,10 +41419,10 @@
     </row>
     <row r="378" hidden="true">
       <c r="A378" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C378" s="2"/>
       <c r="D378" t="s" s="2">
@@ -41441,7 +41445,7 @@
         <v>75</v>
       </c>
       <c r="K378" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L378" s="2"/>
       <c r="M378" s="2"/>
@@ -41494,7 +41498,7 @@
         <v>75</v>
       </c>
       <c r="AF378" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG378" t="s" s="2">
         <v>81</v>
@@ -41514,10 +41518,10 @@
     </row>
     <row r="379" hidden="true">
       <c r="A379" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" t="s" s="2">
@@ -41540,7 +41544,7 @@
         <v>75</v>
       </c>
       <c r="K379" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L379" s="2"/>
       <c r="M379" s="2"/>
@@ -41593,7 +41597,7 @@
         <v>75</v>
       </c>
       <c r="AF379" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG379" t="s" s="2">
         <v>81</v>
@@ -41613,10 +41617,10 @@
     </row>
     <row r="380" hidden="true">
       <c r="A380" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" t="s" s="2">
@@ -41639,7 +41643,7 @@
         <v>75</v>
       </c>
       <c r="K380" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L380" s="2"/>
       <c r="M380" s="2"/>
@@ -41692,7 +41696,7 @@
         <v>75</v>
       </c>
       <c r="AF380" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG380" t="s" s="2">
         <v>81</v>
@@ -41712,10 +41716,10 @@
     </row>
     <row r="381" hidden="true">
       <c r="A381" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" t="s" s="2">
@@ -41738,7 +41742,7 @@
         <v>75</v>
       </c>
       <c r="K381" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L381" s="2"/>
       <c r="M381" s="2"/>
@@ -41791,7 +41795,7 @@
         <v>75</v>
       </c>
       <c r="AF381" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG381" t="s" s="2">
         <v>81</v>
@@ -41811,10 +41815,10 @@
     </row>
     <row r="382" hidden="true">
       <c r="A382" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" t="s" s="2">
@@ -41837,7 +41841,7 @@
         <v>75</v>
       </c>
       <c r="K382" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L382" s="2"/>
       <c r="M382" s="2"/>
@@ -41890,7 +41894,7 @@
         <v>75</v>
       </c>
       <c r="AF382" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG382" t="s" s="2">
         <v>81</v>
@@ -41910,10 +41914,10 @@
     </row>
     <row r="383" hidden="true">
       <c r="A383" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" t="s" s="2">
@@ -41936,7 +41940,7 @@
         <v>75</v>
       </c>
       <c r="K383" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L383" s="2"/>
       <c r="M383" s="2"/>
@@ -41989,7 +41993,7 @@
         <v>75</v>
       </c>
       <c r="AF383" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG383" t="s" s="2">
         <v>81</v>
@@ -42009,13 +42013,13 @@
     </row>
     <row r="384" hidden="true">
       <c r="A384" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D384" t="s" s="2">
         <v>75</v>
@@ -42037,7 +42041,7 @@
         <v>75</v>
       </c>
       <c r="K384" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L384" s="2"/>
       <c r="M384" s="2"/>
@@ -42090,7 +42094,7 @@
         <v>75</v>
       </c>
       <c r="AF384" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG384" t="s" s="2">
         <v>81</v>
@@ -42110,10 +42114,10 @@
     </row>
     <row r="385" hidden="true">
       <c r="A385" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" t="s" s="2">
@@ -42211,10 +42215,10 @@
     </row>
     <row r="386" hidden="true">
       <c r="A386" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" t="s" s="2">
@@ -42312,10 +42316,10 @@
     </row>
     <row r="387" hidden="true">
       <c r="A387" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" t="s" s="2">
@@ -42413,10 +42417,10 @@
     </row>
     <row r="388" hidden="true">
       <c r="A388" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" t="s" s="2">
@@ -42514,10 +42518,10 @@
     </row>
     <row r="389" hidden="true">
       <c r="A389" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" t="s" s="2">
@@ -42617,10 +42621,10 @@
     </row>
     <row r="390" hidden="true">
       <c r="A390" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" t="s" s="2">
@@ -42720,10 +42724,10 @@
     </row>
     <row r="391" hidden="true">
       <c r="A391" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" t="s" s="2">
@@ -42823,10 +42827,10 @@
     </row>
     <row r="392" hidden="true">
       <c r="A392" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" t="s" s="2">
@@ -42926,10 +42930,10 @@
     </row>
     <row r="393" hidden="true">
       <c r="A393" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C393" s="2"/>
       <c r="D393" t="s" s="2">
@@ -43027,10 +43031,10 @@
     </row>
     <row r="394" hidden="true">
       <c r="A394" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C394" s="2"/>
       <c r="D394" t="s" s="2">
@@ -43067,7 +43071,7 @@
         <v>75</v>
       </c>
       <c r="S394" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="T394" t="s" s="2">
         <v>75</v>
@@ -43086,7 +43090,7 @@
       </c>
       <c r="Y394" s="2"/>
       <c r="Z394" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA394" t="s" s="2">
         <v>75</v>
@@ -43104,7 +43108,7 @@
         <v>75</v>
       </c>
       <c r="AF394" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG394" t="s" s="2">
         <v>76</v>
@@ -43124,10 +43128,10 @@
     </row>
     <row r="395" hidden="true">
       <c r="A395" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" t="s" s="2">
@@ -43154,7 +43158,7 @@
       </c>
       <c r="L395" s="2"/>
       <c r="M395" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N395" s="2"/>
       <c r="O395" s="2"/>
@@ -43205,7 +43209,7 @@
         <v>75</v>
       </c>
       <c r="AF395" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG395" t="s" s="2">
         <v>81</v>
@@ -43225,10 +43229,10 @@
     </row>
     <row r="396" hidden="true">
       <c r="A396" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C396" s="2"/>
       <c r="D396" t="s" s="2">
@@ -43255,7 +43259,7 @@
       </c>
       <c r="L396" s="2"/>
       <c r="M396" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N396" s="2"/>
       <c r="O396" s="2"/>
@@ -43306,7 +43310,7 @@
         <v>75</v>
       </c>
       <c r="AF396" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG396" t="s" s="2">
         <v>81</v>
@@ -43326,10 +43330,10 @@
     </row>
     <row r="397" hidden="true">
       <c r="A397" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C397" s="2"/>
       <c r="D397" t="s" s="2">
@@ -43405,7 +43409,7 @@
         <v>75</v>
       </c>
       <c r="AF397" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG397" t="s" s="2">
         <v>81</v>
@@ -43425,10 +43429,10 @@
     </row>
     <row r="398" hidden="true">
       <c r="A398" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C398" s="2"/>
       <c r="D398" t="s" s="2">
@@ -43451,7 +43455,7 @@
         <v>75</v>
       </c>
       <c r="K398" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L398" s="2"/>
       <c r="M398" s="2"/>
@@ -43504,7 +43508,7 @@
         <v>75</v>
       </c>
       <c r="AF398" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG398" t="s" s="2">
         <v>81</v>
@@ -43524,10 +43528,10 @@
     </row>
     <row r="399" hidden="true">
       <c r="A399" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C399" s="2"/>
       <c r="D399" t="s" s="2">
@@ -43550,7 +43554,7 @@
         <v>75</v>
       </c>
       <c r="K399" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L399" s="2"/>
       <c r="M399" s="2"/>
@@ -43603,7 +43607,7 @@
         <v>75</v>
       </c>
       <c r="AF399" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG399" t="s" s="2">
         <v>81</v>
@@ -43623,10 +43627,10 @@
     </row>
     <row r="400" hidden="true">
       <c r="A400" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" t="s" s="2">
@@ -43649,13 +43653,13 @@
         <v>75</v>
       </c>
       <c r="K400" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L400" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N400" s="2"/>
       <c r="O400" s="2"/>
@@ -43706,7 +43710,7 @@
         <v>75</v>
       </c>
       <c r="AF400" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG400" t="s" s="2">
         <v>81</v>
@@ -43726,10 +43730,10 @@
     </row>
     <row r="401" hidden="true">
       <c r="A401" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" t="s" s="2">
@@ -43752,7 +43756,7 @@
         <v>75</v>
       </c>
       <c r="K401" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L401" s="2"/>
       <c r="M401" s="2"/>
@@ -43805,7 +43809,7 @@
         <v>75</v>
       </c>
       <c r="AF401" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG401" t="s" s="2">
         <v>81</v>
@@ -43825,10 +43829,10 @@
     </row>
     <row r="402" hidden="true">
       <c r="A402" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" t="s" s="2">
@@ -43851,7 +43855,7 @@
         <v>75</v>
       </c>
       <c r="K402" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L402" s="2"/>
       <c r="M402" s="2"/>
@@ -43904,7 +43908,7 @@
         <v>75</v>
       </c>
       <c r="AF402" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG402" t="s" s="2">
         <v>81</v>
@@ -43924,10 +43928,10 @@
     </row>
     <row r="403" hidden="true">
       <c r="A403" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" t="s" s="2">
@@ -43950,7 +43954,7 @@
         <v>75</v>
       </c>
       <c r="K403" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L403" s="2"/>
       <c r="M403" s="2"/>
@@ -44003,7 +44007,7 @@
         <v>75</v>
       </c>
       <c r="AF403" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG403" t="s" s="2">
         <v>81</v>
@@ -44023,10 +44027,10 @@
     </row>
     <row r="404" hidden="true">
       <c r="A404" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" t="s" s="2">
@@ -44049,7 +44053,7 @@
         <v>75</v>
       </c>
       <c r="K404" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L404" s="2"/>
       <c r="M404" s="2"/>
@@ -44102,7 +44106,7 @@
         <v>75</v>
       </c>
       <c r="AF404" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG404" t="s" s="2">
         <v>81</v>
@@ -44122,10 +44126,10 @@
     </row>
     <row r="405" hidden="true">
       <c r="A405" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" t="s" s="2">
@@ -44148,7 +44152,7 @@
         <v>75</v>
       </c>
       <c r="K405" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L405" s="2"/>
       <c r="M405" s="2"/>
@@ -44201,7 +44205,7 @@
         <v>75</v>
       </c>
       <c r="AF405" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG405" t="s" s="2">
         <v>81</v>
@@ -44221,10 +44225,10 @@
     </row>
     <row r="406" hidden="true">
       <c r="A406" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" t="s" s="2">
@@ -44247,7 +44251,7 @@
         <v>75</v>
       </c>
       <c r="K406" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L406" s="2"/>
       <c r="M406" s="2"/>
@@ -44300,7 +44304,7 @@
         <v>75</v>
       </c>
       <c r="AF406" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG406" t="s" s="2">
         <v>81</v>
@@ -44320,10 +44324,10 @@
     </row>
     <row r="407" hidden="true">
       <c r="A407" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" t="s" s="2">
@@ -44346,7 +44350,7 @@
         <v>75</v>
       </c>
       <c r="K407" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L407" s="2"/>
       <c r="M407" s="2"/>
@@ -44399,7 +44403,7 @@
         <v>75</v>
       </c>
       <c r="AF407" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG407" t="s" s="2">
         <v>81</v>
@@ -44419,10 +44423,10 @@
     </row>
     <row r="408" hidden="true">
       <c r="A408" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" t="s" s="2">
@@ -44445,7 +44449,7 @@
         <v>75</v>
       </c>
       <c r="K408" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L408" s="2"/>
       <c r="M408" s="2"/>
@@ -44498,7 +44502,7 @@
         <v>75</v>
       </c>
       <c r="AF408" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG408" t="s" s="2">
         <v>81</v>
@@ -44518,10 +44522,10 @@
     </row>
     <row r="409" hidden="true">
       <c r="A409" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" t="s" s="2">
@@ -44544,7 +44548,7 @@
         <v>75</v>
       </c>
       <c r="K409" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L409" s="2"/>
       <c r="M409" s="2"/>
@@ -44597,7 +44601,7 @@
         <v>75</v>
       </c>
       <c r="AF409" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG409" t="s" s="2">
         <v>81</v>
@@ -44617,10 +44621,10 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C410" s="2"/>
       <c r="D410" t="s" s="2">
@@ -44643,13 +44647,13 @@
         <v>75</v>
       </c>
       <c r="K410" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="L410" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N410" s="2"/>
       <c r="O410" s="2"/>
@@ -44700,7 +44704,7 @@
         <v>75</v>
       </c>
       <c r="AF410" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AG410" t="s" s="2">
         <v>81</v>
@@ -44720,10 +44724,10 @@
     </row>
     <row r="411" hidden="true">
       <c r="A411" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C411" s="2"/>
       <c r="D411" t="s" s="2">
@@ -44821,10 +44825,10 @@
     </row>
     <row r="412" hidden="true">
       <c r="A412" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C412" s="2"/>
       <c r="D412" t="s" s="2">
@@ -44922,10 +44926,10 @@
     </row>
     <row r="413" hidden="true">
       <c r="A413" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" t="s" s="2">
@@ -45023,10 +45027,10 @@
     </row>
     <row r="414" hidden="true">
       <c r="A414" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C414" s="2"/>
       <c r="D414" t="s" s="2">
@@ -45124,10 +45128,10 @@
     </row>
     <row r="415" hidden="true">
       <c r="A415" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" t="s" s="2">
@@ -45227,10 +45231,10 @@
     </row>
     <row r="416" hidden="true">
       <c r="A416" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C416" s="2"/>
       <c r="D416" t="s" s="2">
@@ -45330,10 +45334,10 @@
     </row>
     <row r="417" hidden="true">
       <c r="A417" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C417" s="2"/>
       <c r="D417" t="s" s="2">
@@ -45433,10 +45437,10 @@
     </row>
     <row r="418" hidden="true">
       <c r="A418" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C418" s="2"/>
       <c r="D418" t="s" s="2">
@@ -45536,10 +45540,10 @@
     </row>
     <row r="419" hidden="true">
       <c r="A419" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C419" s="2"/>
       <c r="D419" t="s" s="2">
@@ -45637,10 +45641,10 @@
     </row>
     <row r="420" hidden="true">
       <c r="A420" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C420" s="2"/>
       <c r="D420" t="s" s="2">
@@ -45674,7 +45678,7 @@
       </c>
       <c r="Q420" s="2"/>
       <c r="R420" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="S420" t="s" s="2">
         <v>75</v>
@@ -45696,7 +45700,7 @@
       </c>
       <c r="Y420" s="2"/>
       <c r="Z420" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AA420" t="s" s="2">
         <v>75</v>
@@ -45714,7 +45718,7 @@
         <v>75</v>
       </c>
       <c r="AF420" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG420" t="s" s="2">
         <v>81</v>
@@ -45734,10 +45738,10 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C421" s="2"/>
       <c r="D421" t="s" s="2">
@@ -45760,7 +45764,7 @@
         <v>75</v>
       </c>
       <c r="K421" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L421" s="2"/>
       <c r="M421" s="2"/>
@@ -45813,7 +45817,7 @@
         <v>75</v>
       </c>
       <c r="AF421" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG421" t="s" s="2">
         <v>76</v>
@@ -45833,10 +45837,10 @@
     </row>
     <row r="422" hidden="true">
       <c r="A422" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" t="s" s="2">
@@ -45934,10 +45938,10 @@
     </row>
     <row r="423" hidden="true">
       <c r="A423" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C423" s="2"/>
       <c r="D423" t="s" s="2">
@@ -46035,10 +46039,10 @@
     </row>
     <row r="424" hidden="true">
       <c r="A424" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" t="s" s="2">
@@ -46136,10 +46140,10 @@
     </row>
     <row r="425" hidden="true">
       <c r="A425" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C425" s="2"/>
       <c r="D425" t="s" s="2">
@@ -46237,10 +46241,10 @@
     </row>
     <row r="426" hidden="true">
       <c r="A426" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C426" s="2"/>
       <c r="D426" t="s" s="2">
@@ -46340,10 +46344,10 @@
     </row>
     <row r="427" hidden="true">
       <c r="A427" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C427" s="2"/>
       <c r="D427" t="s" s="2">
@@ -46443,10 +46447,10 @@
     </row>
     <row r="428" hidden="true">
       <c r="A428" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C428" s="2"/>
       <c r="D428" t="s" s="2">
@@ -46546,10 +46550,10 @@
     </row>
     <row r="429" hidden="true">
       <c r="A429" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C429" s="2"/>
       <c r="D429" t="s" s="2">
@@ -46649,10 +46653,10 @@
     </row>
     <row r="430" hidden="true">
       <c r="A430" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C430" s="2"/>
       <c r="D430" t="s" s="2">
@@ -46750,10 +46754,10 @@
     </row>
     <row r="431" hidden="true">
       <c r="A431" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C431" s="2"/>
       <c r="D431" t="s" s="2">
@@ -46783,7 +46787,7 @@
       <c r="N431" s="2"/>
       <c r="O431" s="2"/>
       <c r="P431" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q431" s="2"/>
       <c r="R431" t="s" s="2">
@@ -46809,7 +46813,7 @@
       </c>
       <c r="Y431" s="2"/>
       <c r="Z431" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AA431" t="s" s="2">
         <v>75</v>
@@ -46827,7 +46831,7 @@
         <v>75</v>
       </c>
       <c r="AF431" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG431" t="s" s="2">
         <v>81</v>
@@ -46847,10 +46851,10 @@
     </row>
     <row r="432" hidden="true">
       <c r="A432" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C432" s="2"/>
       <c r="D432" t="s" s="2">
@@ -46884,7 +46888,7 @@
       </c>
       <c r="Q432" s="2"/>
       <c r="R432" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="S432" t="s" s="2">
         <v>75</v>
@@ -46906,7 +46910,7 @@
       </c>
       <c r="Y432" s="2"/>
       <c r="Z432" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AA432" t="s" s="2">
         <v>75</v>
@@ -46924,7 +46928,7 @@
         <v>75</v>
       </c>
       <c r="AF432" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG432" t="s" s="2">
         <v>81</v>
@@ -46944,10 +46948,10 @@
     </row>
     <row r="433" hidden="true">
       <c r="A433" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C433" s="2"/>
       <c r="D433" t="s" s="2">
@@ -47003,7 +47007,7 @@
       </c>
       <c r="Y433" s="2"/>
       <c r="Z433" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AA433" t="s" s="2">
         <v>75</v>
@@ -47021,7 +47025,7 @@
         <v>75</v>
       </c>
       <c r="AF433" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG433" t="s" s="2">
         <v>81</v>
@@ -47041,10 +47045,10 @@
     </row>
     <row r="434" hidden="true">
       <c r="A434" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C434" s="2"/>
       <c r="D434" t="s" s="2">
@@ -47120,7 +47124,7 @@
         <v>75</v>
       </c>
       <c r="AF434" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG434" t="s" s="2">
         <v>81</v>
@@ -47140,10 +47144,10 @@
     </row>
     <row r="435" hidden="true">
       <c r="A435" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C435" s="2"/>
       <c r="D435" t="s" s="2">
@@ -47166,7 +47170,7 @@
         <v>75</v>
       </c>
       <c r="K435" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L435" s="2"/>
       <c r="M435" s="2"/>
@@ -47219,7 +47223,7 @@
         <v>75</v>
       </c>
       <c r="AF435" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG435" t="s" s="2">
         <v>81</v>
@@ -47239,10 +47243,10 @@
     </row>
     <row r="436" hidden="true">
       <c r="A436" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C436" s="2"/>
       <c r="D436" t="s" s="2">
@@ -47265,7 +47269,7 @@
         <v>75</v>
       </c>
       <c r="K436" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L436" s="2"/>
       <c r="M436" s="2"/>
@@ -47318,7 +47322,7 @@
         <v>75</v>
       </c>
       <c r="AF436" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AG436" t="s" s="2">
         <v>81</v>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
